--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250001\Desktop\チーム制作\1回目\制作\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13218277-7E39-4168-A5B1-A1466F0250BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA90BEFE-95A7-4BD8-A100-F7786DA5422A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -721,13 +721,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -762,13 +762,13 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -885,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -926,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K12">
         <v>0</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA90BEFE-95A7-4BD8-A100-F7786DA5422A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2756559D-9B1E-4425-A29C-65126A745DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -504,7 +504,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -668,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -706,10 +706,10 @@
         <v>-12.5</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -744,13 +744,13 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>-11.5</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-3.5</v>
+        <v>-5.5</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>-2.5</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>10.5</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>6.5</v>
@@ -867,13 +867,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="C11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>-5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -908,13 +908,13 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>-6.5</v>
+        <v>-10.5</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -949,13 +949,13 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="C13">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -967,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -990,10 +990,10 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="C14">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>0.5</v>
@@ -1008,13 +1008,13 @@
         <v>0</v>
       </c>
       <c r="H14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1064,6 +1064,88 @@
         <v>0</v>
       </c>
       <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>-7.5</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>-7</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>90</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>-3</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>-10.5</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0.5</v>
+      </c>
+      <c r="I17">
+        <v>0.5</v>
+      </c>
+      <c r="J17">
+        <v>0.5</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2756559D-9B1E-4425-A29C-65126A745DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C20717C-E52F-4942-9985-2E780569F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -955,7 +955,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>0</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C20717C-E52F-4942-9985-2E780569F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB062748-C7D2-43D7-A921-966F154E270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -501,7 +501,7 @@
         <v>7.5</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>-25</v>
@@ -542,7 +542,7 @@
         <v>-7.5</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -583,7 +583,7 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -624,7 +624,7 @@
         <v>-25</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>-7</v>
@@ -706,7 +706,7 @@
         <v>-12.5</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>-5.5</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -829,7 +829,7 @@
         <v>10.5</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D10">
         <v>6.5</v>
@@ -870,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
         <v>-5</v>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D12">
         <v>-10.5</v>
@@ -955,7 +955,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1116,7 +1116,7 @@
         <v>-3</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D17">
         <v>-10.5</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB062748-C7D2-43D7-A921-966F154E270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90464582-894C-4EFC-B94A-EDE824C71456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3975" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -706,7 +706,7 @@
         <v>-12.5</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -744,10 +744,10 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -788,7 +788,7 @@
         <v>-5.5</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -829,7 +829,7 @@
         <v>10.5</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>6.5</v>
@@ -870,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>-5</v>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>-10.5</v>
@@ -949,7 +949,7 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>-7.5</v>
+        <v>-7</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -1116,7 +1116,7 @@
         <v>-3</v>
       </c>
       <c r="C17">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>-10.5</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90464582-894C-4EFC-B94A-EDE824C71456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A4954F-562D-4617-BEEF-69FEC673F16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33915" yWindow="-300" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>-7</v>
+        <v>-6.5</v>
       </c>
       <c r="C16">
         <v>2</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB062748-C7D2-43D7-A921-966F154E270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4654DD24-C89A-4D3D-8BB1-64ACB39B380F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="1200" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -662,10 +662,10 @@
         <v>14</v>
       </c>
       <c r="B6">
-        <v>-7.5</v>
+        <v>-8.3000000000000007</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>8.5</v>
@@ -949,7 +949,7 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>2</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4654DD24-C89A-4D3D-8BB1-64ACB39B380F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5838DF-88FD-465C-8247-7262D1783BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -586,7 +586,7 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>2</v>
       </c>
       <c r="D5">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>0</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5838DF-88FD-465C-8247-7262D1783BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E587FB90-A53A-4F86-B5FB-94C6BBDDC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -665,7 +665,7 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D6">
         <v>8.5</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E587FB90-A53A-4F86-B5FB-94C6BBDDC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFD0E81-9945-4C3B-9A39-C3D119D18F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -498,7 +498,7 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>-7.5</v>
+        <v>-6.5</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -703,7 +703,7 @@
         <v>15</v>
       </c>
       <c r="B7">
-        <v>-12.5</v>
+        <v>-8.3000000000000007</v>
       </c>
       <c r="C7">
         <v>0.8</v>
@@ -785,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-5.5</v>
+        <v>-2</v>
       </c>
       <c r="C9">
         <v>0.8</v>
@@ -826,13 +826,13 @@
         <v>15</v>
       </c>
       <c r="B10">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
         <v>0.8</v>
       </c>
       <c r="D10">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -949,19 +949,19 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C13">
         <v>2</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1072,13 +1072,13 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>-7.5</v>
+        <v>-2</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>-7</v>
+        <v>9.5</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1113,13 +1113,13 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="C17">
         <v>0.8</v>
       </c>
       <c r="D17">
-        <v>-10.5</v>
+        <v>-6</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1146,6 +1146,211 @@
         <v>0</v>
       </c>
       <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>-1.5</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>-6</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>-90</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="C19">
+        <v>0.8</v>
+      </c>
+      <c r="D19">
+        <v>-6</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0.5</v>
+      </c>
+      <c r="I19">
+        <v>0.5</v>
+      </c>
+      <c r="J19">
+        <v>0.5</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>6.5</v>
+      </c>
+      <c r="C20">
+        <v>0.8</v>
+      </c>
+      <c r="D20">
+        <v>-2</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.5</v>
+      </c>
+      <c r="I20">
+        <v>0.5</v>
+      </c>
+      <c r="J20">
+        <v>0.5</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>6.5</v>
+      </c>
+      <c r="C21">
+        <v>0.8</v>
+      </c>
+      <c r="D21">
+        <v>15</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0.5</v>
+      </c>
+      <c r="I21">
+        <v>0.5</v>
+      </c>
+      <c r="J21">
+        <v>0.5</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="C22">
+        <v>0.8</v>
+      </c>
+      <c r="D22">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0.5</v>
+      </c>
+      <c r="I22">
+        <v>0.5</v>
+      </c>
+      <c r="J22">
+        <v>0.5</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFD0E81-9945-4C3B-9A39-C3D119D18F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B8B985-71AE-4E1A-B7F7-4D23A770D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -706,7 +706,7 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -788,10 +788,10 @@
         <v>-2</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -829,7 +829,7 @@
         <v>6.5</v>
       </c>
       <c r="C10">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -870,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>-5</v>
@@ -911,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D12">
         <v>-10.5</v>
@@ -1116,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>-6</v>
@@ -1154,7 +1154,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1198,7 +1198,7 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="C19">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>-6</v>
@@ -1239,7 +1239,7 @@
         <v>6.5</v>
       </c>
       <c r="C20">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>-2</v>
@@ -1280,7 +1280,7 @@
         <v>6.5</v>
       </c>
       <c r="C21">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>15</v>
@@ -1318,39 +1318,80 @@
         <v>15</v>
       </c>
       <c r="B22">
-        <v>-8.3000000000000007</v>
+        <v>-6</v>
       </c>
       <c r="C22">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D22">
+        <v>17</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0.5</v>
+      </c>
+      <c r="I22">
+        <v>0.5</v>
+      </c>
+      <c r="J22">
+        <v>0.5</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
         <v>15</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0.5</v>
-      </c>
-      <c r="I22">
-        <v>0.5</v>
-      </c>
-      <c r="J22">
-        <v>0.5</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="B23">
+        <v>-2</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0.5</v>
+      </c>
+      <c r="I23">
+        <v>0.5</v>
+      </c>
+      <c r="J23">
+        <v>0.5</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B8B985-71AE-4E1A-B7F7-4D23A770D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9BDAD0-7E38-4A3F-9D3A-79A770FDC256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -668,13 +668,13 @@
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>8.5</v>
+        <v>-6</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>-6</v>
+        <v>8.5</v>
       </c>
       <c r="E19">
         <v>0</v>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250150\Desktop\2TeamProject1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9BDAD0-7E38-4A3F-9D3A-79A770FDC256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AEB976-FFFF-4DD0-9458-5B3822BA2A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3570" windowWidth="21600" windowHeight="10770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -445,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -668,13 +679,13 @@
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -873,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>-5</v>
+        <v>-5.5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1151,34 +1162,34 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1392,6 +1403,88 @@
         <v>0</v>
       </c>
       <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>-16</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0.5</v>
+      </c>
+      <c r="I24">
+        <v>0.5</v>
+      </c>
+      <c r="J24">
+        <v>0.5</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>-16</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>7</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0.5</v>
+      </c>
+      <c r="I25">
+        <v>0.5</v>
+      </c>
+      <c r="J25">
+        <v>0.5</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,35 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AEB976-FFFF-4DD0-9458-5B3822BA2A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFD0E81-9945-4C3B-9A39-C3D119D18F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7005" yWindow="1140" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -456,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -679,13 +668,13 @@
         <v>1.5</v>
       </c>
       <c r="D6">
-        <v>-10</v>
+        <v>8.5</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -717,7 +706,7 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -758,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D8">
         <v>10</v>
@@ -799,10 +788,10 @@
         <v>-2</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -840,7 +829,7 @@
         <v>6.5</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -881,10 +870,10 @@
         <v>11</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D11">
-        <v>-5.5</v>
+        <v>-5</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -922,7 +911,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D12">
         <v>-10.5</v>
@@ -1127,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D17">
         <v>-6</v>
@@ -1162,34 +1151,34 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18">
+        <v>-1.5</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
         <v>-6</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>-16</v>
-      </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1209,10 +1198,10 @@
         <v>-8.3000000000000007</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D19">
-        <v>8.5</v>
+        <v>-6</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1250,7 +1239,7 @@
         <v>6.5</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D20">
         <v>-2</v>
@@ -1291,7 +1280,7 @@
         <v>6.5</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D21">
         <v>15</v>
@@ -1329,13 +1318,13 @@
         <v>15</v>
       </c>
       <c r="B22">
-        <v>-6</v>
+        <v>-8.3000000000000007</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D22">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1362,129 +1351,6 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23">
-        <v>-2</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>6</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0.5</v>
-      </c>
-      <c r="I23">
-        <v>0.5</v>
-      </c>
-      <c r="J23">
-        <v>0.5</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24">
-        <v>7</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24">
-        <v>-16</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0.5</v>
-      </c>
-      <c r="I24">
-        <v>0.5</v>
-      </c>
-      <c r="J24">
-        <v>0.5</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25">
-        <v>-16</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>7</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0.5</v>
-      </c>
-      <c r="I25">
-        <v>0.5</v>
-      </c>
-      <c r="J25">
-        <v>0.5</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
         <v>0</v>
       </c>
     </row>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFD0E81-9945-4C3B-9A39-C3D119D18F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64764270-4DF3-4D17-87FA-806919B31B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19425" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -96,6 +96,10 @@
   </si>
   <si>
     <t>Goal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stairs</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -445,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -1354,6 +1358,88 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <v>1.3</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>180</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0.6</v>
+      </c>
+      <c r="I23">
+        <v>0.6</v>
+      </c>
+      <c r="J23">
+        <v>0.6</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>0.8</v>
+      </c>
+      <c r="D24">
+        <v>5</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0.5</v>
+      </c>
+      <c r="I24">
+        <v>0.5</v>
+      </c>
+      <c r="J24">
+        <v>0.5</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/Excel/stage2.xlsx
+++ b/Data/Excel/stage2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2250056\OneDrive - yamaguchigakuen\デスクトップ\git\2年生ゲーム制作２回目\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64764270-4DF3-4D17-87FA-806919B31B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CF96B7-2E12-4CCA-B4EF-E49C825705DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>type</t>
     <phoneticPr fontId="1"/>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="11" max="11" width="10.5" customWidth="1"/>
@@ -713,7 +713,7 @@
         <v>0.8</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -959,7 +959,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1205,7 +1205,7 @@
         <v>0.8</v>
       </c>
       <c r="D19">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1437,6 +1437,47 @@
         <v>0</v>
       </c>
       <c r="M24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25">
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>-6</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
     </row>
